--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.538178128442702</v>
+        <v>1.062453945871939</v>
       </c>
       <c r="D2" t="n">
-        <v>5.274638493738828</v>
+        <v>0.8571287552325596</v>
       </c>
       <c r="E2" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F2" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.619031090245226</v>
+        <v>0.4255925521648493</v>
       </c>
       <c r="D3" t="n">
-        <v>3.128305691772613</v>
+        <v>0.5083496749130496</v>
       </c>
       <c r="E3" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F3" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.19487236882113</v>
+        <v>2.631666759933434</v>
       </c>
       <c r="D4" t="n">
-        <v>17.63442395531976</v>
+        <v>2.865593892739461</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F4" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.00767361800967</v>
+        <v>3.738746962926571</v>
       </c>
       <c r="D5" t="n">
-        <v>24.51218684185741</v>
+        <v>3.98323036180183</v>
       </c>
       <c r="E5" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F5" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.15109633707158</v>
+        <v>2.299553154774132</v>
       </c>
       <c r="D6" t="n">
-        <v>13.45740034692119</v>
+        <v>2.186827556374694</v>
       </c>
       <c r="E6" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F6" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.82107008188743</v>
+        <v>2.408423888306708</v>
       </c>
       <c r="D7" t="n">
-        <v>11.88689134892058</v>
+        <v>1.931619844199594</v>
       </c>
       <c r="E7" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F7" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.94053097512675</v>
+        <v>5.840336283458097</v>
       </c>
       <c r="D8" t="n">
-        <v>37.42208178495787</v>
+        <v>6.081088290055654</v>
       </c>
       <c r="E8" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F8" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.94318246923633</v>
+        <v>2.753267151250903</v>
       </c>
       <c r="D9" t="n">
-        <v>16.93601141383823</v>
+        <v>2.752101854748712</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F9" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.0946279927678</v>
+        <v>4.402877048824768</v>
       </c>
       <c r="D10" t="n">
-        <v>27.06348929020688</v>
+        <v>4.397817009658618</v>
       </c>
       <c r="E10" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F10" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.80195903279979</v>
+        <v>5.167818342829967</v>
       </c>
       <c r="D11" t="n">
-        <v>31.76826512987881</v>
+        <v>5.162343083605307</v>
       </c>
       <c r="E11" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F11" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.12960643365496</v>
+        <v>4.733561045468931</v>
       </c>
       <c r="D12" t="n">
-        <v>29.09554014536115</v>
+        <v>4.728025273621187</v>
       </c>
       <c r="E12" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F12" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.07450313908706</v>
+        <v>3.262106760101648</v>
       </c>
       <c r="D13" t="n">
-        <v>20.76962449373299</v>
+        <v>3.375063980231612</v>
       </c>
       <c r="E13" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F13" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.42900364240866</v>
+        <v>5.107213091891408</v>
       </c>
       <c r="D14" t="n">
-        <v>31.22412609498582</v>
+        <v>5.073920490435196</v>
       </c>
       <c r="E14" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F14" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.9162459305207</v>
+        <v>6.811389963709614</v>
       </c>
       <c r="D15" t="n">
-        <v>42.6096953417623</v>
+        <v>6.924075493036374</v>
       </c>
       <c r="E15" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F15" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>52.34882214966316</v>
+        <v>8.506683599320265</v>
       </c>
       <c r="D16" t="n">
-        <v>53.04715918660855</v>
+        <v>8.620163367823888</v>
       </c>
       <c r="E16" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F16" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>45.24911587067786</v>
+        <v>7.352981328985153</v>
       </c>
       <c r="D17" t="n">
-        <v>45.8157930503509</v>
+        <v>7.445066370682021</v>
       </c>
       <c r="E17" t="n">
-        <v>13.4658108017784</v>
+        <v>2.18819425528899</v>
       </c>
       <c r="F17" t="n">
-        <v>13.90034610084694</v>
+        <v>2.258806241387627</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
